--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T11:49:33+00:00</t>
+    <t>2026-06-18T12:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-healthcare-activity|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-healthcareservice-healthcare-activity|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -376,7 +376,7 @@
     <t>as-ext-data-trace</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-data-trace|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -506,7 +506,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>HealthcareService.meta.extension:as-ext-data-trace.extension:date-maj-ae</t>
@@ -638,7 +638,7 @@
     <t>as-dr-canonical</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-healthcare-activity|1.2.0-snapshot-1</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-dr-healthcareservice-healthcare-activity|1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>HealthcareService.meta.security</t>
@@ -790,7 +790,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1053,7 +1053,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:07:50+00:00</t>
+    <t>2026-06-18T13:08:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-frcore-2.2.0/ig/StructureDefinition-as-dr-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:08:38+00:00</t>
+    <t>2026-06-18T13:31:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
